--- a/Day15_Task/Copy of String_Function_Excel_Exercises(1).xlsx
+++ b/Day15_Task/Copy of String_Function_Excel_Exercises(1).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="308">
   <si>
     <t>ID</t>
   </si>
@@ -494,12 +494,6 @@
     <t>9871203456</t>
   </si>
   <si>
-    <t>EMP-CHN-7134</t>
-  </si>
-  <si>
-    <t>Training completed</t>
-  </si>
-  <si>
     <t>Aishwarya D</t>
   </si>
   <si>
@@ -507,12 +501,6 @@
   </si>
   <si>
     <t>9803456721</t>
-  </si>
-  <si>
-    <t>EMP-SLM-9023</t>
-  </si>
-  <si>
-    <t>Probation extended</t>
   </si>
   <si>
     <t>Kavin G</t>
@@ -1329,10 +1317,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.35">
@@ -1361,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J2" t="str">
         <f>LEFT(B2,3)</f>
@@ -1394,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J3" t="str">
         <f>RIGHT(B3,4)</f>
@@ -1427,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J4" t="str">
         <f>UPPER(E3)</f>
@@ -1460,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J5" t="str">
         <f>PROPER(B40)</f>
@@ -1493,7 +1481,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J6">
         <f>LEN(B7)</f>
@@ -1526,7 +1514,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J7" t="str">
         <f>MID(C10,FIND("@",C10)+1,LEN(C10))</f>
@@ -1559,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J8" t="str">
         <f>LEFT(C10,FIND("@",C10)-1)</f>
@@ -1592,7 +1580,7 @@
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J9" t="str">
         <f>RIGHT(D9,4)</f>
@@ -1625,7 +1613,7 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J10" t="str">
         <f>"*******" &amp; RIGHT(D10,3)</f>
@@ -1658,7 +1646,7 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J11" t="str">
         <f>B2 &amp; ", " &amp; E2</f>
@@ -1691,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="I12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J12" t="str">
         <f>MID(F2, 5, 3)</f>
@@ -1724,7 +1712,7 @@
         <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J13" t="str">
         <f>RIGHT(F2, LEN(F2)-8)</f>
@@ -1757,7 +1745,7 @@
         <v>13</v>
       </c>
       <c r="I14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J14" t="str">
         <f>IF(ISNUMBER(SEARCH("gmail", C2)), "Yes", "No")</f>
@@ -1790,7 +1778,7 @@
         <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J15">
         <f>FIND("@", C2)</f>
@@ -1823,7 +1811,7 @@
         <v>15</v>
       </c>
       <c r="I16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J16" t="str">
         <f>MID(C15, FIND("@", C15)+1, LEN(C15))</f>
@@ -1856,7 +1844,7 @@
         <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J17" t="str">
         <f>UPPER(LEFT(B2,3) &amp; RIGHT(D2,2))</f>
@@ -1889,7 +1877,7 @@
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J18" t="str">
         <f>SUBSTITUTE(B2,"."," ")</f>
@@ -1922,7 +1910,7 @@
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J19" t="str">
         <f>SUBSTITUTE(F2,"-"," ")</f>
@@ -1955,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J20" t="str">
         <f>LEFT(B2,5)</f>
@@ -1988,7 +1976,7 @@
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J21" t="str">
         <f>LEFT(B2,1)&amp;MID(B2,FIND(" ",B2)+1,1)</f>
@@ -2021,7 +2009,7 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J22" t="str">
         <f>B2&amp;"-"&amp;E2&amp;"-"&amp;F2</f>
@@ -2054,7 +2042,7 @@
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J23">
         <f>LEN(SUBSTITUTE(B2," "," "))</f>
@@ -2087,7 +2075,7 @@
         <v>23</v>
       </c>
       <c r="I24" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.45" x14ac:dyDescent="0.35">
@@ -2116,7 +2104,7 @@
         <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J25" t="str">
         <f>SUBSTITUTE(F2,"EMP-","")</f>
@@ -2149,7 +2137,7 @@
         <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J26" t="str">
         <f>UPPER(LEFT(G2,1))&amp;LOWER(MID(G2,2,LEN(G2)))</f>
@@ -2182,7 +2170,7 @@
         <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J27" t="str">
         <f>TRIM(RIGHT(G2,LEN(G2)-FIND(" ",G2,LEN(G2)-LEN(SUBSTITUTE(G2," ","")))))</f>
@@ -2215,7 +2203,7 @@
         <v>27</v>
       </c>
       <c r="I28" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J28" t="str">
         <f>LEFT(C2,FIND(".",C2,FIND("@",C2))-1)</f>
@@ -2248,7 +2236,7 @@
         <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J29" t="str">
         <f>TRIM(RIGHT(B2,LEN(B2)-FIND(" ",B2))&amp;" "&amp;LEFT(B2,FIND(" ",B2)-1))</f>
@@ -2281,7 +2269,7 @@
         <v>29</v>
       </c>
       <c r="I30" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J30">
         <f>LEN(B12)-LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B12,"a",""),"e",""),"i",""),"o",""),"u",""))</f>
@@ -2304,17 +2292,11 @@
       <c r="E31" t="s">
         <v>10</v>
       </c>
-      <c r="F31" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" t="s">
-        <v>160</v>
-      </c>
       <c r="H31">
         <v>30</v>
       </c>
       <c r="I31" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J31" t="str">
         <f>TRIM(MID(G2,FIND(" ",G2)+1,FIND(" ",G2,FIND(" ",G2)+1-FIND(" ",G2))))</f>
@@ -2326,28 +2308,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" t="s">
         <v>161</v>
-      </c>
-      <c r="C32" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" t="s">
-        <v>163</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
       </c>
-      <c r="F32" t="s">
-        <v>164</v>
-      </c>
-      <c r="G32" t="s">
-        <v>165</v>
-      </c>
       <c r="H32">
         <v>31</v>
       </c>
       <c r="I32" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J32" t="str">
         <f>MID(F2,5,3)</f>
@@ -2359,28 +2335,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H33">
         <v>32</v>
       </c>
       <c r="I33" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J33" t="str">
         <f>LOWER(SUBSTITUTE(B2," ",""))&amp;RIGHT(F2,4)</f>
@@ -2392,32 +2368,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
         <v>45</v>
       </c>
       <c r="F34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H34">
         <v>33</v>
       </c>
       <c r="I34" t="s">
-        <v>294</v>
-      </c>
-      <c r="J34" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31,"0",""),"1",""),"2",""),"3",""),"4",""),"5",""),"6",""),"7",""),"8",""),"9","")</f>
-        <v>EMP-CHN-</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2425,28 +2397,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D35" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
         <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H35">
         <v>34</v>
       </c>
       <c r="I35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J35" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F2,"E",""),"M",""),"P",""),"-",""),"C","")</f>
@@ -2458,28 +2430,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H36">
         <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J36" t="str">
         <f>IF(LEN(B2)&gt;10,"Yes","No")</f>
@@ -2491,28 +2463,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H37">
         <v>36</v>
       </c>
       <c r="I37" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J37" t="str">
         <f>SUBSTITUTE(LEFT(C2,FIND("@",C2)-1),".","")</f>
@@ -2524,28 +2496,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G38" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H38">
         <v>37</v>
       </c>
       <c r="I38" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J38" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(D2," ",""),"-","")</f>
@@ -2557,28 +2529,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
         <v>45</v>
       </c>
       <c r="F39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H39">
         <v>38</v>
       </c>
       <c r="I39" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J39" t="str">
         <f>"******"&amp;RIGHT(C39,11)</f>
@@ -2590,28 +2562,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D40" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E40" t="s">
         <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G40" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H40">
         <v>39</v>
       </c>
       <c r="I40" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J40" t="str">
         <f>LEFT(B28,4)&amp;RIGHT(B28,4)</f>
@@ -2623,28 +2595,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
         <v>34</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H41">
         <v>40</v>
       </c>
       <c r="I41" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J41" t="str">
         <f>LEFT(B2,FIND(" ",B2))&amp;UPPER(RIGHT(B2,LEN(B2)-FIND(" ",B2)))</f>
@@ -2656,28 +2628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D42" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G42" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H42">
         <v>41</v>
       </c>
       <c r="I42" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J42" t="str">
         <f>E45&amp;RIGHT(D45,3)</f>
@@ -2689,28 +2661,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G43" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H43">
         <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J43" t="str">
         <f>MID(B2,ROUNDUP(LEN(B2)/2,0),IF(MOD(LEN(B2),2)=0,2,1))</f>
@@ -2722,28 +2694,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E44" t="s">
         <v>45</v>
       </c>
       <c r="F44" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G44" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H44">
         <v>43</v>
       </c>
       <c r="I44" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J44" t="str">
         <f>SUBSTITUTE(G37,E37,UPPER(E37))</f>
@@ -2755,28 +2727,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E45" t="s">
         <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G45" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H45">
         <v>44</v>
       </c>
       <c r="I45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J45" t="str">
         <f>LEFT(G2,1)&amp;MID(G2,FIND(" ",G2)+1,1)</f>
@@ -2788,28 +2760,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
       </c>
       <c r="F46" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G46" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H46">
         <v>45</v>
       </c>
       <c r="I46" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J46" t="str">
         <f>LEFT(B2,1)&amp;MID(B2,FIND(" ",B2)+1,1)&amp;MID(F2,5,3)</f>
@@ -2821,28 +2793,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H47">
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J47" t="str">
         <f>IF(ISNUMBER(FIND(".",C2)),"Yes","No")</f>
@@ -2854,28 +2826,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G48" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H48">
         <v>47</v>
       </c>
       <c r="I48" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J48" t="str">
         <f>LEFT(B2,FIND(" ",B2)-1)</f>
@@ -2887,28 +2859,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D49" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E49" t="s">
         <v>22</v>
       </c>
       <c r="F49" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G49" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H49">
         <v>48</v>
       </c>
       <c r="I49" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J49" t="str">
         <f>TRIM(RIGHT(SUBSTITUTE(B2," ",REPT(" ",50)),50))</f>
@@ -2920,19 +2892,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D50" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G50" t="s">
         <v>41</v>
@@ -2941,7 +2913,7 @@
         <v>49</v>
       </c>
       <c r="I50" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J50" t="str">
         <f>"91-"&amp;D34</f>
@@ -2953,28 +2925,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D51" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G51" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H51">
         <v>50</v>
       </c>
       <c r="I51" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J51">
         <f>LEN(TRIM(G2))-LEN(SUBSTITUTE(TRIM(G2)," ",""))+1</f>
@@ -2997,10 +2969,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3011,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3019,7 +2991,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3027,7 +2999,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3035,7 +3007,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3043,7 +3015,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3051,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3059,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3067,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3075,7 +3047,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3083,7 +3055,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3091,7 +3063,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3099,7 +3071,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3107,7 +3079,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3115,7 +3087,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.45" x14ac:dyDescent="0.35">
@@ -3123,7 +3095,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3131,7 +3103,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3139,7 +3111,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3147,7 +3119,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3155,7 +3127,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3163,7 +3135,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3171,7 +3143,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3179,7 +3151,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3187,7 +3159,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3195,7 +3167,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3203,7 +3175,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3211,7 +3183,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3219,7 +3191,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3227,7 +3199,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3235,7 +3207,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3243,7 +3215,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3251,7 +3223,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3259,7 +3231,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3267,7 +3239,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3275,7 +3247,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3283,7 +3255,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3291,7 +3263,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3299,7 +3271,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3307,7 +3279,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3315,7 +3287,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3323,7 +3295,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3331,7 +3303,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3339,7 +3311,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3347,7 +3319,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3355,7 +3327,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
@@ -3363,7 +3335,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -3371,7 +3343,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -3379,7 +3351,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -3387,7 +3359,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -3395,7 +3367,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -3403,7 +3375,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
